--- a/data/trans_orig/P3A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27733</t>
+          <t>27703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>19807</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30777</t>
+          <t>30529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38920</t>
+          <t>39093</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56054</t>
+          <t>55699</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28729</t>
+          <t>28759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>39894</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20594</t>
+          <t>20842</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32278</t>
+          <t>31564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51779</t>
+          <t>52134</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68913</t>
+          <t>68740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103567</t>
+          <t>102910</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130641</t>
+          <t>130710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122207</t>
+          <t>121606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152825</t>
+          <t>152311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>231689</t>
+          <t>235330</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>270879</t>
+          <t>273841</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179676</t>
+          <t>179607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206750</t>
+          <t>207407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>200811</t>
+          <t>201325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231429</t>
+          <t>232030</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>393074</t>
+          <t>390112</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>432264</t>
+          <t>428623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31481</t>
+          <t>31739</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48522</t>
+          <t>49600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19107</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34818</t>
+          <t>34635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56612</t>
+          <t>54350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79666</t>
+          <t>78185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88059</t>
+          <t>86981</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105100</t>
+          <t>104842</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88724</t>
+          <t>88907</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104435</t>
+          <t>103231</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180457</t>
+          <t>181938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203511</t>
+          <t>205773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>79,11%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160825</t>
+          <t>161434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>194731</t>
+          <t>195904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172522</t>
+          <t>170832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206363</t>
+          <t>207188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>344083</t>
+          <t>343708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>397200</t>
+          <t>389694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308628</t>
+          <t>307455</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342534</t>
+          <t>341925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>322186</t>
+          <t>321361</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>356027</t>
+          <t>357717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>634708</t>
+          <t>642214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>687825</t>
+          <t>688200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>24034</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36365</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23597</t>
+          <t>24199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36666</t>
+          <t>36851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51796</t>
+          <t>50484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69196</t>
+          <t>68471</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31562</t>
+          <t>31450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25424</t>
+          <t>25239</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>37891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48378</t>
+          <t>49103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65778</t>
+          <t>67090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>57,06%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92926</t>
+          <t>93502</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121053</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99181</t>
+          <t>99557</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128826</t>
+          <t>127512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>203036</t>
+          <t>200919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242401</t>
+          <t>239763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183600</t>
+          <t>183507</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211727</t>
+          <t>211151</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210967</t>
+          <t>212281</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240612</t>
+          <t>240236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402045</t>
+          <t>404683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>441410</t>
+          <t>443527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20938</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36658</t>
+          <t>35997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29094</t>
+          <t>30319</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47730</t>
+          <t>48303</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55522</t>
+          <t>54954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78908</t>
+          <t>76907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80169</t>
+          <t>80830</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95889</t>
+          <t>96004</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89168</t>
+          <t>88595</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107804</t>
+          <t>106579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174817</t>
+          <t>176818</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198203</t>
+          <t>198771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>146023</t>
+          <t>148578</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180617</t>
+          <t>181319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163677</t>
+          <t>165504</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200904</t>
+          <t>202389</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>322566</t>
+          <t>323044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>370197</t>
+          <t>373546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296348</t>
+          <t>295646</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>330942</t>
+          <t>328387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>337877</t>
+          <t>336392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>375104</t>
+          <t>373277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>645549</t>
+          <t>642200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>693180</t>
+          <t>692702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>21791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>23857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>39477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,97%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20232</t>
+          <t>20622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>30417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>29446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>39717</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>52401</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67270</t>
+          <t>68021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110106</t>
+          <t>108647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139512</t>
+          <t>139270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116667</t>
+          <t>116404</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147483</t>
+          <t>147849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>233485</t>
+          <t>233704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>276436</t>
+          <t>274681</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>209210</t>
+          <t>209452</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238616</t>
+          <t>240075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>232383</t>
+          <t>232017</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>263199</t>
+          <t>263462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452152</t>
+          <t>453907</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495103</t>
+          <t>494884</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25304</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41570</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32107</t>
+          <t>32332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49361</t>
+          <t>50578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61158</t>
+          <t>61172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85452</t>
+          <t>85510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94457</t>
+          <t>94373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110723</t>
+          <t>111030</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90569</t>
+          <t>89352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107823</t>
+          <t>107598</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190505</t>
+          <t>190447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214799</t>
+          <t>214785</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,83%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>152738</t>
+          <t>154519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189092</t>
+          <t>189234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>171826</t>
+          <t>171223</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>209631</t>
+          <t>207722</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>333531</t>
+          <t>334332</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>387098</t>
+          <t>382916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>336298</t>
+          <t>336156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372652</t>
+          <t>370871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361402</t>
+          <t>363311</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>399207</t>
+          <t>399810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>709325</t>
+          <t>713507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>762892</t>
+          <t>762091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25905</t>
+          <t>26162</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46040</t>
+          <t>46302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>38397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51205</t>
+          <t>51280</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68587</t>
+          <t>70657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93917</t>
+          <t>93690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28773</t>
+          <t>28516</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>23607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48095</t>
+          <t>46025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>385603</t>
+          <t>384341</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>413909</t>
+          <t>413815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>429923</t>
+          <t>430897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>459924</t>
+          <t>461211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>825124</t>
+          <t>825876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>868038</t>
+          <t>867435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46601</t>
+          <t>46695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74907</t>
+          <t>76169</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56695</t>
+          <t>55408</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86696</t>
+          <t>85722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109091</t>
+          <t>109694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152005</t>
+          <t>151253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126652</t>
+          <t>126229</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139162</t>
+          <t>139012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156689</t>
+          <t>156896</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171479</t>
+          <t>171638</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287581</t>
+          <t>287204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307488</t>
+          <t>306712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22899</t>
+          <t>23322</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25412</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45319</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>549818</t>
+          <t>549081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>589738</t>
+          <t>588310</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>637741</t>
+          <t>637030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>674181</t>
+          <t>673605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1197153</t>
+          <t>1202937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1253761</t>
+          <t>1252753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>76428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114920</t>
+          <t>115657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>88367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124231</t>
+          <t>124942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172949</t>
+          <t>173957</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229557</t>
+          <t>223773</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25124</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19206</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30755</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48,91%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37,39%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>59,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>21828</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16568</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27703</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16432</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>28349</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>38,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>25124</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19807</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>30529</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>48,91%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>39564</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55699</t>
+          <t>56258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26247</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20616</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32165</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40,13%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62,61%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>34634</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28759</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39894</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28113</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>40030</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>61,34%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>50,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>70,66%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26247</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>20842</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31564</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>51,09%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52134</t>
+          <t>51575</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68740</t>
+          <t>68269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>136638</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>121287</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>150630</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>38,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>42,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>116138</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>102910</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>130710</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>101622</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>130011</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>37,43%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>33,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>42,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>136638</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>121606</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>152311</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>38,64%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>235330</t>
+          <t>232650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>273841</t>
+          <t>272348</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>216998</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>203006</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>232349</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>61,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>57,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>65,7%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>292</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>194179</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>179607</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>207407</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>180306</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>208695</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>62,57%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>57,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>66,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>216998</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>201325</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>232030</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>61,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390112</t>
+          <t>391605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>428623</t>
+          <t>431303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26921</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19803</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>34644</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>40073</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31739</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49600</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>32070</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>49068</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,24%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>26921</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20311</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>34635</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>56073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>79080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>96621</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>88898</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>103739</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,21%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>71,96%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>83,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>96508</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>86981</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>104842</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>87513</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>104511</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>70,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,76%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>96621</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>88907</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>103231</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,21%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>181938</t>
+          <t>181043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205773</t>
+          <t>204050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>172022</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>207056</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>32,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>39,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>178038</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>161434</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>195904</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>160422</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>195426</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>35,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,07%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>188683</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>170832</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>207188</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>343708</t>
+          <t>343940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>389694</t>
+          <t>392042</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>339866</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>321493</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>356527</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>482</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>325321</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>307455</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>341925</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>307933</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>342937</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>64,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>339866</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>321361</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>357717</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>64,3%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>642214</t>
+          <t>639866</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>688200</t>
+          <t>687968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30270</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23945</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36105</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29872</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24034</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36159</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35588</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>53,84%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,17%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>30270</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24199</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>36851</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>48,75%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50484</t>
+          <t>51613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68471</t>
+          <t>68544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31820</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25985</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38145</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25612</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19325</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>31450</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19896</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>32632</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>46,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,83%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>31820</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25239</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>37891</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>51,25%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49103</t>
+          <t>49030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67090</t>
+          <t>65961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>113715</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>99569</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>128386</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>37,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>106228</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>93502</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>121146</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>91889</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>119232</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,87%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>113715</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>99557</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>127512</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>33,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>200919</t>
+          <t>200164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>239763</t>
+          <t>241304</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>226078</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>211407</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>240224</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>62,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,7%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>198425</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>183507</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>211151</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>185421</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>212764</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>226078</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>212281</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>240236</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>66,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>404683</t>
+          <t>403142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>443527</t>
+          <t>444282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37880</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29719</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>47917</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>27,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>27834</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20823</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35997</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>20438</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>35834</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>23,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,81%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>37880</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>30319</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>48303</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54954</t>
+          <t>54969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76907</t>
+          <t>78802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99018</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>88981</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>107179</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>72,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>65,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>88993</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>80830</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>96004</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>80993</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>96389</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>76,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>69,19%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,18%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99018</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>88595</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>106579</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>72,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176818</t>
+          <t>174923</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198771</t>
+          <t>198756</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>181865</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>162166</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>200479</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>163934</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>148578</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>181319</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>147102</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>181161</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>34,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>181865</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>165504</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>202389</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,75%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>323044</t>
+          <t>322120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>373546</t>
+          <t>370964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>356916</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>338302</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>376615</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>450</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>313031</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>295646</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>328387</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>295804</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>329863</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>65,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>356916</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>336392</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>373277</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,25%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>642200</t>
+          <t>644782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>692702</t>
+          <t>693626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16714</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11448</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22159</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>14846</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10224</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20019</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10420</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20152</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>36,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,26%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16714</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11520</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21791</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>24215</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39477</t>
+          <t>39930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34523</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29078</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39789</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>56,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25795</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20622</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30417</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>20489</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>30221</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>50,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>34523</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>29446</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>39717</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52401</t>
+          <t>51948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68021</t>
+          <t>67663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>131810</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>116678</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>147988</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>38,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>123792</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>108647</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>139270</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>108489</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>138190</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>35,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>131810</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>116404</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>147849</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>34,7%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>233704</t>
+          <t>235955</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>274681</t>
+          <t>277891</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>248056</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>231878</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>263188</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>61,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>342</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>224930</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>209452</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>240075</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>210532</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>240233</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>64,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>248056</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>232017</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>263462</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>65,3%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>453907</t>
+          <t>450697</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>494884</t>
+          <t>492633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40408</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32113</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>49462</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,88%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>32346</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>24997</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41654</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>25391</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>41180</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>23,78%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>40408</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>32332</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>50578</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61172</t>
+          <t>60746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85510</t>
+          <t>84266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99522</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>90468</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>107817</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>71,12%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>77,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>103681</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>94373</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>111030</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>94847</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>110636</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>76,22%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>69,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99522</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>89352</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>107598</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>71,12%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190447</t>
+          <t>191691</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214785</t>
+          <t>215211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>170425</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>208535</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>170985</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>154519</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>189234</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>152883</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>188892</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>32,54%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>188932</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>171223</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>207722</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,09%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>334332</t>
+          <t>333384</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>382916</t>
+          <t>386607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>382101</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>362498</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>400608</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>70,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>354405</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>336156</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>370871</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>336498</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>372507</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>67,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>382101</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>363311</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>399810</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>66,91%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>713507</t>
+          <t>709816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>762091</t>
+          <t>763039</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,59%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41893</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35307</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46822</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>73,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>62,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>82,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>38631</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26162</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46302</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>70,65%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>45489</t>
+          <t>37613</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38397</t>
+          <t>31824</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51280</t>
+          <t>41272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>84121</t>
+          <t>79507</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70657</t>
+          <t>70974</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93690</t>
+          <t>86443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14839</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9910</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21425</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,47%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16047</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8376</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28516</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29,35%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23607</t>
+          <t>14934</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32561</t>
+          <t>23983</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22992</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46025</t>
+          <t>32516</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>563</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>408110</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>394619</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>421508</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>82,96%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>88,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>399607</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>384341</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>413815</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>86,77%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>83,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>445828</t>
+          <t>373396</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>430897</t>
+          <t>360453</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>461211</t>
+          <t>384853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>845435</t>
+          <t>781506</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>825876</t>
+          <t>762266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>867435</t>
+          <t>799746</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>67568</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>54170</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>81059</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>60903</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46695</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76169</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>70791</t>
+          <t>59052</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55408</t>
+          <t>47595</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85722</t>
+          <t>71995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>131694</t>
+          <t>126620</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109694</t>
+          <t>108380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151253</t>
+          <t>145860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>151863</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>143653</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>157590</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>85,3%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>93,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>133328</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>126229</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>139012</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>89,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>84,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>92,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>165297</t>
+          <t>133941</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156896</t>
+          <t>126714</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171638</t>
+          <t>139349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>298625</t>
+          <t>285803</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287204</t>
+          <t>274830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>306712</t>
+          <t>293734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16223</t>
+          <t>16556</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23322</t>
+          <t>24766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>16035</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26453</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>34275</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45696</t>
+          <t>43565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>601865</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>583378</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>616585</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>83,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>816</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>571565</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>549081</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>588310</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>85,98%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>82,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>88,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>656615</t>
+          <t>544950</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>637030</t>
+          <t>529731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>673605</t>
+          <t>559865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1228181</t>
+          <t>1146815</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1202937</t>
+          <t>1125822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1252753</t>
+          <t>1168626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98964</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>84244</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>117451</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>93173</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>76428</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>115657</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14,02%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>105357</t>
+          <t>84232</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88367</t>
+          <t>69317</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124942</t>
+          <t>99451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>198529</t>
+          <t>183196</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173957</t>
+          <t>161385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223773</t>
+          <t>204189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
